--- a/data/conflict_report.xlsx
+++ b/data/conflict_report.xlsx
@@ -451,64 +451,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TP012345</t>
+          <t>TP067890</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Test Student</t>
+          <t>Test Student 3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>Demo Lecturer 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>Demo Lecturer 3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Slot Not Assigned</t>
+          <t>No Common Availability</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Available slot exists but no presentation slot assigned.</t>
+          <t>Supervisor and 2nd Marker do not have matching available slots.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TP067890</t>
+          <t>TP015826</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Test Student 3</t>
+          <t>Test Student 4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Demo Lecturer 1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Demo Lecturer 2</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>No Common Availability</t>
+          <t>Slot Not Assigned</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Supervisor and 2nd Marker do not have matching available slots.</t>
+          <t>Available slot exists but no presentation slot assigned.</t>
         </is>
       </c>
     </row>
